--- a/config/mappings/psi.xlsx
+++ b/config/mappings/psi.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,21 @@
           <t>Destination UID</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +506,9 @@
           <t>DEST_OU_PSI_x1WE</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
